--- a/src/test/resources/charlesriverTA.xlsx
+++ b/src/test/resources/charlesriverTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejaskadu/git/charlesriver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3401794C-1B9B-1B48-B592-42B50CF31A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB4738C-3450-C544-A578-6D57758770F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{86A8A38D-0014-D14C-A537-4363CB3C4FC3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Assumptions and given" sheetId="1" r:id="rId1"/>
     <sheet name="Manual Test Cases" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -145,9 +145,6 @@
     <t>Total assets 100% vested no cash drag or no transaction fees</t>
   </si>
   <si>
-    <t>Stock pricess are static as given and no market movement was adjusted in calculation</t>
-  </si>
-  <si>
     <t>No rebalancing threshold was considered in calculation and balancing is absolute</t>
   </si>
   <si>
@@ -279,13 +276,16 @@
 HD-&gt;HOLD-&gt;0</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Execution </t>
-  </si>
-  <si>
     <t>Manual test cases are created assuming Application APIs are exposed to perform relevant operation</t>
   </si>
   <si>
     <t>Automated test cases are created with tech stack Cucumber BDD , Junit,Rest Assured , Java, Allure report</t>
+  </si>
+  <si>
+    <t>Stock prices are static as given and no market movement was adjusted in calculation</t>
+  </si>
+  <si>
+    <t>Test Execution  --&gt; https://github.com/tejasykadu0911/pf-rebalancing-restassured-bdd</t>
   </si>
 </sst>
 </file>
@@ -432,15 +432,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -459,7 +458,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -912,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
@@ -920,7 +919,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -928,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -936,12 +935,12 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -949,7 +948,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -957,193 +956,187 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
     </row>
     <row r="14" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:10" ht="97" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>20</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="11">
         <v>10</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>-10</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <v>150</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <f>(100000*F16/100)/G16</f>
         <v>-66.666666666666671</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <v>20</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="11">
         <v>20</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <v>0</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <v>90</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <f>(100000*F17/100)/G17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <v>20</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <v>30</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="11">
         <v>10</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <v>220</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <f>(100000*F18/100)/G18</f>
         <v>45.454545454545453</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>20</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="11">
         <v>20</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <v>0</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <v>450</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <f>(100000*F19/100)/G19</f>
         <v>0</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <v>20</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="11">
         <v>20</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>0</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="12">
         <v>70</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f>(100000*F20/100)/G20</f>
         <v>0</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="1"/>
     </row>
@@ -1162,233 +1155,233 @@
   <dimension ref="A2:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="4"/>
-    <col min="2" max="2" width="31" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="46.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="39.33203125" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="10.83203125" style="3"/>
+    <col min="2" max="2" width="31" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="46.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="119" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="D9" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="119" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="E11" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="119" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+      <c r="E14" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="B15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/charlesriverTA.xlsx
+++ b/src/test/resources/charlesriverTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejaskadu/git/charlesriver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB4738C-3450-C544-A578-6D57758770F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1820258-2771-E349-87EB-F1775D7A1D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{86A8A38D-0014-D14C-A537-4363CB3C4FC3}"/>
   </bookViews>
@@ -279,13 +279,13 @@
     <t>Manual test cases are created assuming Application APIs are exposed to perform relevant operation</t>
   </si>
   <si>
-    <t>Automated test cases are created with tech stack Cucumber BDD , Junit,Rest Assured , Java, Allure report</t>
-  </si>
-  <si>
     <t>Stock prices are static as given and no market movement was adjusted in calculation</t>
   </si>
   <si>
     <t>Test Execution  --&gt; https://github.com/tejasykadu0911/pf-rebalancing-restassured-bdd</t>
+  </si>
+  <si>
+    <t>Automated test cases are created with tech stack Cucumber BDD , Junit,Rest Assured , Java, Allure report, wiremock for portfolio app stub</t>
   </si>
 </sst>
 </file>
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
@@ -1136,7 +1136,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="1"/>
     </row>

--- a/src/test/resources/charlesriverTA.xlsx
+++ b/src/test/resources/charlesriverTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejaskadu/git/charlesriver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1820258-2771-E349-87EB-F1775D7A1D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F763AA-A41E-0440-BF4D-E24B69F04042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{86A8A38D-0014-D14C-A537-4363CB3C4FC3}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="77">
   <si>
     <t>Account- ABC with $100K in total asset (100% is vested)</t>
   </si>
@@ -111,11 +111,6 @@
   </si>
   <si>
     <t>Perform rebalance  for account CRD001</t>
-  </si>
-  <si>
-    <t>Portfolio should show securities target is not not balanced
-IBM shows -10% variance
-ORCL shows 10% variance</t>
   </si>
   <si>
     <t>Stock = (Total assets(100K) * variance/100)  / unit price</t>
@@ -172,11 +167,6 @@
 HD-&gt;HOLD-&gt;0</t>
   </si>
   <si>
-    <t>Portfolio balance should execute trades for  
-IBM Buy 66-67 IBM shares,
-ORCL Sell 45-26 shares, No trades on other securities MSFT,AAPL,HD</t>
-  </si>
-  <si>
     <t>Check Portfolio CRD001 is not balanced</t>
   </si>
   <si>
@@ -205,9 +195,6 @@
   </si>
   <si>
     <t>Verify assets are greater than 0</t>
-  </si>
-  <si>
-    <t>API should throw an error "Invalid total assets" in case of assets less than or equal to zero</t>
   </si>
   <si>
     <t>Verify if there is no duplicate security</t>
@@ -286,6 +273,22 @@
   </si>
   <si>
     <t>Automated test cases are created with tech stack Cucumber BDD , Junit,Rest Assured , Java, Allure report, wiremock for portfolio app stub</t>
+  </si>
+  <si>
+    <t>Portfolio should show securities target is not balanced
+IBM shows -10% variance
+ORCL shows 10% variance</t>
+  </si>
+  <si>
+    <t>Portfolio balance should execute trades for  
+IBM Buy 66 IBM shares,
+ORCL Sell 45 shares, No trades on other securities MSFT,AAPL,HD</t>
+  </si>
+  <si>
+    <t>API should throw an error "Invalid total assets" in case of assets greater than zero</t>
+  </si>
+  <si>
+    <t>Please go through README.md to understand tech stack in detail.</t>
   </si>
 </sst>
 </file>
@@ -499,13 +502,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>109066</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -879,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDAD271-5CC6-2C49-ADBD-D93485D176E7}">
-  <dimension ref="B2:J23"/>
+  <dimension ref="B2:J24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
@@ -887,7 +890,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -895,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
@@ -903,7 +906,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
@@ -911,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
@@ -919,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -927,7 +930,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -935,12 +938,12 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -948,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -956,160 +959,137 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:10" ht="97" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:10" ht="97" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="10"/>
-      <c r="C16" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="11">
-        <v>20</v>
-      </c>
-      <c r="E16" s="11">
-        <v>10</v>
-      </c>
-      <c r="F16" s="11">
-        <v>-10</v>
-      </c>
-      <c r="G16" s="12">
-        <v>150</v>
-      </c>
-      <c r="H16" s="13">
-        <f>(100000*F16/100)/G16</f>
-        <v>-66.666666666666671</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="13">
-        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10"/>
       <c r="C17" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="11">
         <v>20</v>
       </c>
       <c r="E17" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F17" s="11">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G17" s="12">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="H17" s="13">
         <f>(100000*F17/100)/G17</f>
-        <v>0</v>
+        <v>-66.666666666666671</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="13">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10"/>
       <c r="C18" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="11">
         <v>20</v>
       </c>
       <c r="E18" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F18" s="11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="H18" s="13">
         <f>(100000*F18/100)/G18</f>
-        <v>45.454545454545453</v>
+        <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="13">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10"/>
       <c r="C19" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="11">
         <v>20</v>
       </c>
       <c r="E19" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F19" s="11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G19" s="12">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="H19" s="13">
         <f>(100000*F19/100)/G19</f>
-        <v>0</v>
+        <v>45.454545454545453</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" s="13">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10"/>
       <c r="C20" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="11">
         <v>20</v>
@@ -1121,28 +1101,56 @@
         <v>0</v>
       </c>
       <c r="G20" s="12">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="H20" s="13">
         <f>(100000*F20/100)/G20</f>
         <v>0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J20" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="1"/>
+    <row r="21" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="11">
+        <v>20</v>
+      </c>
+      <c r="E21" s="11">
+        <v>20</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>70</v>
+      </c>
+      <c r="H21" s="13">
+        <f>(100000*F21/100)/G21</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="13">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C24" s="1"/>
+      <c r="D24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1182,41 +1190,41 @@
     </row>
     <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>22</v>
@@ -1228,12 +1236,12 @@
         <v>19</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>18</v>
@@ -1242,7 +1250,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>21</v>
@@ -1250,138 +1258,138 @@
     </row>
     <row r="8" spans="1:5" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
